--- a/Paris_out.xlsx
+++ b/Paris_out.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Multi-story gourmet food market/destination</t>
+          <t>Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Le Grand Epicerie de Paris | Multi-story gourmet food market/destination</t>
+          <t>Le Grand Epicerie de Paris | Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
         </is>
       </c>
     </row>
@@ -1855,6 +1855,270 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>&lt;a href='https://www.parisunlocked.com/paris-neighbourhoods/canal-st-martin-and-republique/paris-canal-saint-martin-neighborhood-guide/' target='_blank'&gt;Canal Saint-Martin&lt;/a&gt; | One of the Right Bank’s most vibrant areas. Scores of boutiques, restaurants and wine bars, and a bustling nightlife scene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Puces D'Aligre (flea market)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Flea market/vintage (runs on weekdays, most others are weekend-only). Plenty of random art, books, china, maybe a cool ashtray? Plus, lots of good options for lunch afterward in the area. Mostly outdoors, so not for a rainy day.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>flea market</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>48.84893978148027, 2.378808817868072</t>
+        </is>
+      </c>
+      <c r="E47">
+        <v>2.37880881786807</v>
+      </c>
+      <c r="F47">
+        <v>48.8489397814803</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Puces D'Aligre (flea market) | Flea market/vintage (runs on weekdays, most others are weekend-only). Plenty of random art, books, china, maybe a cool ashtray? Plus, lots of good options for lunch afterward in the area. Mostly outdoors, so not for a rainy day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Musee du Parfum - Fragonard</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Small Museum showcasing history of perfumery and olfactory science. Free version or paid tour. Not a must-do but said to be pretty interesting.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Museum</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>48.8716411945289, 2.330882908084299</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>2.3308829080843</v>
+      </c>
+      <c r="F48">
+        <v>48.8716411945289</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Musee du Parfum - Fragonard | Small Museum showcasing history of perfumery and olfactory science. Free version or paid tour. Not a must-do but said to be pretty interesting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Marche Mouffetard</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Wednesdays (morning). Old-skool historic street/farmers market, very Parisian.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>48.84054368023993, 2.3502561755405686</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>2.35025617554057</v>
+      </c>
+      <c r="F49">
+        <v>48.8405436802399</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Marche Mouffetard | Wednesdays (morning). Old-skool historic street/farmers market, very Parisian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Armagnac Casterede</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This one is just for Hambone, if we're in the area. </t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Armagnac shop</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>48.87557552982641, 2.314988438928556</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>2.31498843892856</v>
+      </c>
+      <c r="F50">
+        <v>48.8755755298264</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Armagnac Casterede | This one is just for Hambone, if we're in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Maison Ryst-Dupeyron</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Possibly a better option (they also bottle their own).</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cognac/Armagnac</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>48.85493306265429, 2.3255801891860908</t>
+        </is>
+      </c>
+      <c r="E51">
+        <v>2.32558018918609</v>
+      </c>
+      <c r="F51">
+        <v>48.8549330626543</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Maison Ryst-Dupeyron | Possibly a better option (they also bottle their own).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mamiche (boulangerie)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sandwhiches, bread</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>48.88025108038357, 2.343552628836084</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>2.34355262883608</v>
+      </c>
+      <c r="F52">
+        <v>48.8802510803836</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Mamiche (boulangerie) | Sandwhiches, bread</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jardins des Archives Nationales</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Quiet green space with shrub-lined gravel paths &amp; seasonal flowers, overlooked by elegant buildings.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>park</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>48.86010411759876, 2.357299404095819</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>2.35729940409582</v>
+      </c>
+      <c r="F53">
+        <v>48.8601041175988</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Jardins des Archives Nationales | Quiet green space with shrub-lined gravel paths &amp; seasonal flowers, overlooked by elegant buildings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Marché couvert des Enfants Rouges</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>48.86462477434395, 2.3620981386226587</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>2.36209813862266</v>
+      </c>
+      <c r="F54">
+        <v>48.864624774344</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Marché couvert des Enfants Rouges | Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
         </is>
       </c>
     </row>

--- a/Paris_out.xlsx
+++ b/Paris_out.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gourmet market</t>
+          <t>market</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>flea market</t>
+          <t>market</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Museum</t>
+          <t>museum</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Armagnac shop</t>
+          <t>Armagnac</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cognac/Armagnac</t>
+          <t>Armagnac</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">

--- a/Paris_out.xlsx
+++ b/Paris_out.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -885,7 +885,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LALA Hôtel</t>
+          <t>&lt;a href='https://www.lalahotel.com/' target='_blank'&gt;LALA Hôtel&lt;/a&gt;</t>
         </is>
       </c>
       <c r="B17" t="e">
@@ -909,7 +909,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LALA Hôtel |</t>
+          <t>&lt;a href='https://www.lalahotel.com/' target='_blank'&gt;LALA Hôtel&lt;/a&gt; |</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,8 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)</t>
+          <t>Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)
+Dev &amp; Joel visted, May 25, 2026.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1326,7 +1327,8 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Place de la Concorde | Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)</t>
+          <t>Place de la Concorde | Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)
+Dev &amp; Joel visted, May 25, 2026.</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1538,8 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rooftop bar behind the windmill blades at Moulen Rouge</t>
+          <t>Rooftop bar behind the windmill blades at Moulen Rouge
+Visted May 25, 2026, sat behind the blades of the windmill. Big fun.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1557,7 +1560,8 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>&lt;a href='https://www.lamachinedumoulinrouge.com/le-bar-a-bulles/' target='_blank'&gt;Le Bar à Bulles&lt;/a&gt; | Rooftop bar behind the windmill blades at Moulen Rouge</t>
+          <t>&lt;a href='https://www.lamachinedumoulinrouge.com/le-bar-a-bulles/' target='_blank'&gt;Le Bar à Bulles&lt;/a&gt; | Rooftop bar behind the windmill blades at Moulen Rouge
+Visted May 25, 2026, sat behind the blades of the windmill. Big fun.</t>
         </is>
       </c>
     </row>
@@ -2119,6 +2123,311 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>Marché couvert des Enfants Rouges | Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Les Domaines Qui Montent Paris Cardinet</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Wine store</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>48.882116, 2.328847</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>2.328847</v>
+      </c>
+      <c r="F55">
+        <v>48.882116</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Les Domaines Qui Montent Paris Cardinet | Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Cafe l'Entracte</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>48.884068, 2.326317</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>2.326317</v>
+      </c>
+      <c r="F56">
+        <v>48.884068</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cafe l'Entracte | So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>&lt;a href='https://www.rooster-restaurant.com/reservation/' target='_blank'&gt;ROOSTER PAR FRÉDÉRIC DUCA&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After training in prestigious houses (from Passedat to Darroze), Frédéric Duca has set up shop in the more working-class part of the 17th arrondissement. In a former street corner cafe, the Marseille-born chef signs dishes which pay numerous tributes to his Mediterranean and Provençal roots. The lunchtime menu is at delicious eater-friendly prices. More ambitious in the evenings.
+Vistined Thursday, May 21, 2026. </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>48.88687437146972, 2.3131238164807524</t>
+        </is>
+      </c>
+      <c r="E57">
+        <v>2.31312381648075</v>
+      </c>
+      <c r="F57">
+        <v>48.8868743714697</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>&lt;a href='https://www.rooster-restaurant.com/reservation/' target='_blank'&gt;ROOSTER PAR FRÉDÉRIC DUCA&lt;/a&gt; | After training in prestigious houses (from Passedat to Darroze), Frédéric Duca has set up shop in the more working-class part of the 17th arrondissement. In a former street corner cafe, the Marseille-born chef signs dishes which pay numerous tributes to his Mediterranean and Provençal roots. The lunchtime menu is at delicious eater-friendly prices. More ambitious in the evenings.
+Vistined Thursday, May 21, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Le Wagon Bleu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Corsican cuisine in a wood-paneled railway carriage which becomes a late-night club on the weekend.
+Great meal with excellent dose of Clementine liquor at meal's end.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>48.883029954751635, 2.320535551879477</t>
+        </is>
+      </c>
+      <c r="E58">
+        <v>2.32053555187948</v>
+      </c>
+      <c r="F58">
+        <v>48.8830299547516</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Le Wagon Bleu | Corsican cuisine in a wood-paneled railway carriage which becomes a late-night club on the weekend.
+Great meal with excellent dose of Clementine liquor at meal's end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>La Samaritaine</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FANCY department store. </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>48.859038971904695, 2.342141408689555</t>
+        </is>
+      </c>
+      <c r="E59">
+        <v>2.34214140868955</v>
+      </c>
+      <c r="F59">
+        <v>48.8590389719047</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>La Samaritaine | FANCY department store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Big Love</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BigLove is a Neapolitan trattoria created by the cheerful Big Mamma team. Through the big glass door on rue Debeylleme, customers are warmly welcomed into an authentic, intimate setting with the feel of a large Italian grocery shop and cosy cafés. BigLove also offers gourmet brunches and traditional Neapolitan dishes, all 100% vegaterian!
+Visted May 19, 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>48.86246746812821, 2.3636752266517496</t>
+        </is>
+      </c>
+      <c r="E60">
+        <v>2.36367522665175</v>
+      </c>
+      <c r="F60">
+        <v>48.8624674681282</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Big Love | BigLove is a Neapolitan trattoria created by the cheerful Big Mamma team. Through the big glass door on rue Debeylleme, customers are warmly welcomed into an authentic, intimate setting with the feel of a large Italian grocery shop and cosy cafés. BigLove also offers gourmet brunches and traditional Neapolitan dishes, all 100% vegaterian!
+Visted May 19, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Habib Beirut</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lebanese restaurant
+Visited May 17, 2026. Excellent wine, inexpensive, great flavors.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>48.880146211484224, 2.321841803042917</t>
+        </is>
+      </c>
+      <c r="E61">
+        <v>2.32184180304292</v>
+      </c>
+      <c r="F61">
+        <v>48.8801462114842</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Habib Beirut | Lebanese restaurant
+Visited May 17, 2026. Excellent wine, inexpensive, great flavors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Crazy-busy discount drugstore, with floors of toilettries.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>48.85290456181854, 2.3333528975762388</t>
+        </is>
+      </c>
+      <c r="E62">
+        <v>2.33335289757624</v>
+      </c>
+      <c r="F62">
+        <v>48.8529045618185</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt; | Crazy-busy discount drugstore, with floors of toilettries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VETRA - Vêtement de travail depuis 1927 - Paris</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fancy French "workwear" https://www.vetra.fr/fr/vestes-de-travail-homme/2556-veste-workwear-moleskine-authentique-made-in-france.html</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>48.8616663, 2.3647518</t>
+        </is>
+      </c>
+      <c r="E63">
+        <v>2.3647518</v>
+      </c>
+      <c r="F63">
+        <v>48.8616663</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>VETRA - Vêtement de travail depuis 1927 - Paris | Fancy French "workwear" https://www.vetra.fr/fr/vestes-de-travail-homme/2556-veste-workwear-moleskine-authentique-made-in-france.html</t>
         </is>
       </c>
     </row>
